--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487521_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487521_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6395</v>
+        <v>3.8005</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4303</v>
+        <v>0.6339</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2091</v>
+        <v>3.1666</v>
       </c>
       <c r="G2" t="n">
         <v>1.7454</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>7.9818</v>
+        <v>3.1429</v>
       </c>
       <c r="T2" t="n">
-        <v>5.8413</v>
+        <v>2.0449</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1404</v>
+        <v>1.0979</v>
       </c>
       <c r="V2" t="n">
         <v>0.6749000000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>D. ONWUKA ONWUKA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9636</v>
+        <v>3.655</v>
       </c>
       <c r="E3" t="n">
-        <v>1.769</v>
+        <v>4.9739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1946</v>
+        <v>-1.3189</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4308</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7842</v>
+        <v>0.7381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3534</v>
+        <v>3.112</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9965</v>
+        <v>5.098</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6643</v>
+        <v>2.164</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6677999999999999</v>
+        <v>2.934</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5657</v>
+        <v>-1.248</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8801</v>
+        <v>-1.4259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3144</v>
+        <v>0.178</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9843</v>
+        <v>0.8328</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5445</v>
+        <v>0.3205</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5602</v>
+        <v>0.5123</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2664</v>
+        <v>-0.0486</v>
       </c>
       <c r="W3" t="n">
-        <v>1.492</v>
+        <v>1.7097</v>
       </c>
       <c r="X3" t="n">
         <v>-1.7583</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ONWUKA ONWUKA</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9207</v>
+        <v>3.3757</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3465</v>
+        <v>3.2346</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4258</v>
+        <v>0.1411</v>
       </c>
       <c r="G4" t="n">
-        <v>3.85</v>
+        <v>2.4308</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7381</v>
+        <v>2.7842</v>
       </c>
       <c r="I4" t="n">
-        <v>3.112</v>
+        <v>-0.3534</v>
       </c>
       <c r="J4" t="n">
-        <v>5.098</v>
+        <v>2.9965</v>
       </c>
       <c r="K4" t="n">
-        <v>2.164</v>
+        <v>3.6643</v>
       </c>
       <c r="L4" t="n">
-        <v>2.934</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.248</v>
+        <v>-0.5657</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4259</v>
+        <v>-0.8801</v>
       </c>
       <c r="O4" t="n">
-        <v>0.178</v>
+        <v>0.3144</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9015</v>
+        <v>0.4279</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3068</v>
+        <v>-0.0788</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4054</v>
+        <v>0.5067</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0486</v>
+        <v>-0.2664</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7097</v>
+        <v>1.492</v>
       </c>
       <c r="X4" t="n">
         <v>-1.7583</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2371</v>
+        <v>1.9126</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6088</v>
+        <v>-0.3877</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8459</v>
+        <v>2.3003</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2905</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0599</v>
+        <v>0.6156</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1764</v>
+        <v>0.3976</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2364</v>
+        <v>0.2181</v>
       </c>
       <c r="V5" t="n">
         <v>1.2166</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9349</v>
+        <v>1.5765</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6958</v>
+        <v>-0.3466</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6308</v>
+        <v>1.9232</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1664</v>
+        <v>2.4677</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4397</v>
+        <v>-0.5641</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2733</v>
+        <v>3.0319</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8435</v>
+        <v>1.4929</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9647</v>
+        <v>-0.5683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1212</v>
+        <v>2.0612</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3229</v>
+        <v>0.9749</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.475</v>
+        <v>0.0042</v>
       </c>
       <c r="O6" t="n">
-        <v>0.152</v>
+        <v>0.9707</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3709</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3975</v>
+        <v>-0.1525</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1476</v>
+        <v>-0.2935</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2498</v>
+        <v>0.141</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3329</v>
+        <v>-0.1512</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3329</v>
+        <v>-0.7595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6077</v>
+        <v>1.4188</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1818</v>
+        <v>-0.3724</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7895</v>
+        <v>1.7912</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4677</v>
+        <v>-1.1664</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5641</v>
+        <v>-1.4397</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0319</v>
+        <v>0.2733</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4929</v>
+        <v>-0.8435</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5683</v>
+        <v>-0.9647</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0612</v>
+        <v>0.1212</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9749</v>
+        <v>-0.3229</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0042</v>
+        <v>-0.475</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9707</v>
+        <v>0.152</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1213</v>
+        <v>0.8813</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1286</v>
+        <v>0.4711</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0074</v>
+        <v>0.4102</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1512</v>
+        <v>0.3329</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7595</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2076</v>
+        <v>-0.6365</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1184</v>
+        <v>-2.5473</v>
       </c>
       <c r="F8" t="n">
         <v>1.9108</v>
@@ -1078,10 +1078,10 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0353</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.4217</v>
       </c>
       <c r="U8" t="n">
         <v>0.1141</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8917</v>
+        <v>-2.1182</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5708</v>
+        <v>-1.1751</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3209</v>
+        <v>-0.9431</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9747</v>
+        <v>-2.2755</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8435</v>
+        <v>-0.5577</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1313</v>
+        <v>-1.7178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0408</v>
+        <v>-1.2016</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0408</v>
+        <v>0.1225</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.3241</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0156</v>
+        <v>-1.0739</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8843</v>
+        <v>-0.6802</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1313</v>
+        <v>-0.3938</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.1573</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5634</v>
+        <v>0.0265</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3029</v>
+        <v>0.1309</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.602</v>
+        <v>-2.3813</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4986</v>
+        <v>-0.9802</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1034</v>
+        <v>-1.4011</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2755</v>
+        <v>-0.9747</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5577</v>
+        <v>-0.8435</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7178</v>
+        <v>-0.1313</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2016</v>
+        <v>0.0408</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1225</v>
+        <v>0.0408</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3241</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0739</v>
+        <v>-1.0156</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6802</v>
+        <v>-0.8843</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3938</v>
+        <v>-0.1313</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3265</v>
+        <v>0.3768</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.297</v>
+        <v>0.1541</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0295</v>
+        <v>0.2228</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.6022</v>
+        <v>10.6031</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8716</v>
+        <v>3.033099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7306</v>
+        <v>7.5701</v>
       </c>
       <c r="G11" t="n">
         <v>4.332499999999999</v>
@@ -1282,13 +1282,13 @@
         <v>1.2244</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1083</v>
+        <v>3.108299999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>6.055999999999999</v>
+        <v>6.056</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9396</v>
+        <v>4.939600000000001</v>
       </c>
       <c r="L11" t="n">
         <v>1.1163</v>
@@ -1312,13 +1312,13 @@
         <v>10.5757</v>
       </c>
       <c r="S11" t="n">
-        <v>5.8169</v>
+        <v>6.8179</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3024</v>
+        <v>3.464100000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5143</v>
+        <v>3.354</v>
       </c>
       <c r="V11" t="n">
         <v>1.607</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.7703</v>
+        <v>5.7971</v>
       </c>
       <c r="E12" t="n">
         <v>4.3536</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4168</v>
+        <v>1.4435</v>
       </c>
       <c r="G12" t="n">
         <v>3.4052</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0063</v>
+        <v>0.0204</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2217</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2154</v>
+        <v>0.2422</v>
       </c>
       <c r="V12" t="n">
         <v>1.5881</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8257</v>
+        <v>0.3171</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8916</v>
+        <v>1.7614</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0659</v>
+        <v>-1.4443</v>
       </c>
       <c r="G13" t="n">
-        <v>0.511</v>
+        <v>2.6383</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.096</v>
+        <v>1.098</v>
       </c>
       <c r="I13" t="n">
-        <v>1.607</v>
+        <v>1.5402</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1725</v>
+        <v>3.2123</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2825</v>
+        <v>1.5668</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4549</v>
+        <v>1.6455</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6615</v>
+        <v>-0.574</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8135</v>
+        <v>-0.4687</v>
       </c>
       <c r="O13" t="n">
-        <v>0.152</v>
+        <v>-0.1053</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9792</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9792</v>
+        <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1657</v>
+        <v>-1.279</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7191</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4466</v>
+        <v>-0.6656</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8302</v>
+        <v>-0.4546</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8302</v>
+        <v>-2.5549</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2126</v>
+        <v>-0.3195</v>
       </c>
       <c r="E14" t="n">
         <v>-0.0176</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.195</v>
+        <v>-0.302</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3019</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0893</v>
+        <v>-0.0176</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2081</v>
+        <v>0.1012</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2794</v>
+        <v>-0.3859</v>
       </c>
       <c r="E15" t="n">
-        <v>1.352</v>
+        <v>-3.1279</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6314</v>
+        <v>2.742</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6383</v>
+        <v>-0.1452</v>
       </c>
       <c r="H15" t="n">
-        <v>1.098</v>
+        <v>-0.5545</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5402</v>
+        <v>0.4093</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2123</v>
+        <v>-0.4337</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5668</v>
+        <v>0.1225</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6455</v>
+        <v>-0.5562</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.574</v>
+        <v>0.2885</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4687</v>
+        <v>-0.677</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1053</v>
+        <v>0.9655</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8755</v>
+        <v>-0.9066</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0228</v>
+        <v>-0.7358</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8527</v>
+        <v>-0.1708</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4546</v>
+        <v>0.6659</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5549</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8441</v>
+        <v>-0.9499</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.6396</v>
+        <v>1.3566</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7955</v>
+        <v>-2.3064</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1452</v>
+        <v>0.511</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5545</v>
+        <v>-1.096</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4093</v>
+        <v>1.607</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4337</v>
+        <v>1.1725</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1225</v>
+        <v>-0.2825</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5562</v>
+        <v>1.4549</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2885</v>
+        <v>-0.6615</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.677</v>
+        <v>-0.8135</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9655</v>
+        <v>0.152</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3648</v>
+        <v>0.3901</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2474</v>
+        <v>0.1841</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1174</v>
+        <v>0.206</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6659</v>
+        <v>-2.8302</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>-2.8302</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.542</v>
+        <v>-1.2571</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1905</v>
+        <v>-0.9859</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3515</v>
+        <v>-0.2713</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9485</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3769</v>
+        <v>-1.092</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8316</v>
+        <v>-0.627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5453</v>
+        <v>-0.4651</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3275</v>
+        <v>-2.1854</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9055</v>
+        <v>-2.4962</v>
       </c>
       <c r="F18" t="n">
-        <v>0.578</v>
+        <v>0.3107</v>
       </c>
       <c r="G18" t="n">
         <v>-3.112</v>
@@ -1858,13 +1858,13 @@
         <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9728</v>
+        <v>-0.8307</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8446</v>
+        <v>-0.4352</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1282</v>
+        <v>-0.3955</v>
       </c>
       <c r="V18" t="n">
         <v>-0.397</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. LOPEZ CAMIÑA</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5445</v>
+        <v>-2.5799</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4729</v>
+        <v>-1.6162</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0716</v>
+        <v>-0.9637</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1057</v>
+        <v>-1.8669</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4291</v>
+        <v>0.1546</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6767</v>
+        <v>-2.0215</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5172</v>
+        <v>-0.3347</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9562</v>
+        <v>0.49</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.8246</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5886</v>
+        <v>-1.5323</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4729</v>
+        <v>-0.3354</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1157</v>
+        <v>-1.1969</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4399</v>
+        <v>-0.5326</v>
       </c>
       <c r="T19" t="n">
-        <v>0.414</v>
+        <v>-0.3023</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.854</v>
+        <v>-0.2302</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3905</v>
+        <v>0.2113</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>B. LOPEZ CAMIÑA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.145</v>
+        <v>-2.8912</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1279</v>
+        <v>-3.0869</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0172</v>
+        <v>0.1957</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8669</v>
+        <v>-2.1057</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1546</v>
+        <v>-1.4291</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0215</v>
+        <v>-0.6767</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3347</v>
+        <v>-1.5172</v>
       </c>
       <c r="K20" t="n">
-        <v>0.49</v>
+        <v>-0.9562</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8246</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5323</v>
+        <v>-0.5886</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3354</v>
+        <v>-0.4729</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1969</v>
+        <v>-0.1157</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>0.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0977</v>
+        <v>-0.7866</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2837</v>
+        <v>-0.5867</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2113</v>
+        <v>-0.3905</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2614</v>
+        <v>-4.1056</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0661</v>
+        <v>-2.9638</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1952</v>
+        <v>-1.1418</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4957</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6113</v>
+        <v>-0.4555</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.517</v>
+        <v>-0.4146</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0409</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.560499999999999</v>
+        <v>-8.560299999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.8229</v>
+        <v>-6.822899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7375</v>
+        <v>-1.7376</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.421400000000001</v>
+        <v>-3.4214</v>
       </c>
       <c r="H22" t="n">
         <v>-0.6668000000000001</v>
@@ -2143,16 +2143,16 @@
         <v>-2.755</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7974</v>
+        <v>2.797400000000001</v>
       </c>
       <c r="K22" t="n">
         <v>4.3955</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.598200000000001</v>
+        <v>-1.5982</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.219100000000001</v>
+        <v>-6.219099999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-5.0621</v>
@@ -2170,13 +2170,13 @@
         <v>12.73</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.4902</v>
+        <v>-5.490099999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.4848</v>
+        <v>-3.4847</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.0055</v>
+        <v>-2.0054</v>
       </c>
       <c r="V22" t="n">
         <v>-1.607</v>
@@ -2185,7 +2185,7 @@
         <v>4.636099999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.243200000000001</v>
+        <v>-6.2432</v>
       </c>
     </row>
   </sheetData>
